--- a/resources/school/school_ability.xlsx
+++ b/resources/school/school_ability.xlsx
@@ -4441,7 +4441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="18.375" customWidth="1" style="8" min="1" max="2"/>
@@ -6019,6 +6019,22 @@
         <v>1</v>
       </c>
       <c r="G78" s="0" t="n">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="n">
+        <v>8010002</v>
+      </c>
+      <c r="B79" s="0" t="n"/>
+      <c r="C79" s="0" t="n"/>
+      <c r="D79" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="0" t="n">
         <v>901</v>
       </c>
     </row>

--- a/resources/school/school_ability.xlsx
+++ b/resources/school/school_ability.xlsx
@@ -385,7 +385,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -434,6 +434,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -986,7 +989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
@@ -1177,17 +1180,17 @@
       <c r="A5" s="16" t="n">
         <v>1001</v>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>御剑</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>每回合自动凝聚飞剑，暴击时飞剑追击敌方造成额外伤害并施加内伤。飞剑越多后续爆发越强。</t>
         </is>
       </c>
-      <c r="D5" s="17" t="n"/>
+      <c r="D5" s="18" t="n"/>
       <c r="E5" s="11" t="n"/>
       <c r="F5" s="11" t="n"/>
       <c r="G5" s="11" t="n">
@@ -1224,12 +1227,12 @@
       <c r="A6" s="16" t="n">
         <v>1002</v>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>诛仙</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>燃烧气血连出三段强力剑击，威力逐段递增，释放后需休息恢复。</t>
         </is>
@@ -1270,17 +1273,17 @@
       <c r="A7" s="16" t="n">
         <v>1003</v>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>万剑</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>驱使飞剑齐射多个敌方，攻击中有概率额外获得飞剑。</t>
         </is>
       </c>
-      <c r="D7" s="17" t="n"/>
+      <c r="D7" s="18" t="n"/>
       <c r="G7" s="11" t="n">
         <v>1</v>
       </c>
@@ -1315,17 +1318,17 @@
       <c r="A8" s="16" t="n">
         <v>1004</v>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>杀意</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>进入杀意状态提升攻击力，击败敌方后自动追斩气血最低的目标。</t>
         </is>
       </c>
-      <c r="D8" s="17" t="n"/>
+      <c r="D8" s="18" t="n"/>
       <c r="G8" s="11" t="n">
         <v>1</v>
       </c>
@@ -1360,17 +1363,17 @@
       <c r="A9" s="16" t="n">
         <v>1005</v>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>剑魄</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>飞剑获得灵性可触发暴击，使飞剑追击的伤害大幅提升。</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n"/>
+      <c r="D9" s="18" t="n"/>
       <c r="G9" s="11" t="n">
         <v>1</v>
       </c>
@@ -1405,17 +1408,17 @@
       <c r="A10" s="16" t="n">
         <v>1006</v>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>天罡护体</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>以罡气护身，受物理攻击时有概率格挡并自动反击。</t>
         </is>
       </c>
-      <c r="D10" s="17" t="n"/>
+      <c r="D10" s="18" t="n"/>
       <c r="G10" s="11" t="n">
         <v>1</v>
       </c>
@@ -1450,17 +1453,17 @@
       <c r="A11" s="16" t="n">
         <v>1007</v>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>追风</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>迅捷一击后进入神速状态，持续提升自身速度。</t>
         </is>
       </c>
-      <c r="D11" s="17" t="n"/>
+      <c r="D11" s="18" t="n"/>
       <c r="G11" s="11" t="n">
         <v>1</v>
       </c>
@@ -1495,17 +1498,17 @@
       <c r="A12" s="16" t="n">
         <v>1008</v>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>破军</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>全力蓄劲提升攻击力后，对单体造成一记破甲重击。</t>
         </is>
       </c>
-      <c r="D12" s="17" t="n"/>
+      <c r="D12" s="18" t="n"/>
       <c r="G12" s="11" t="n">
         <v>1</v>
       </c>
@@ -1540,17 +1543,17 @@
       <c r="A13" s="16" t="n">
         <v>1009</v>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>生死决</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>与敌方进入生死对决，双方交替攻击直到一方倒下。</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n"/>
+      <c r="D13" s="18" t="n"/>
       <c r="G13" s="11" t="n">
         <v>1</v>
       </c>
@@ -1585,17 +1588,17 @@
       <c r="A14" s="16" t="n">
         <v>2001</v>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>驭风</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>每次施法积累风势，风势满溢后进入狂风状态，获得额外行动机会。</t>
         </is>
       </c>
-      <c r="D14" s="17" t="n"/>
+      <c r="D14" s="18" t="n"/>
       <c r="G14" s="11" t="n">
         <v>1</v>
       </c>
@@ -1630,17 +1633,17 @@
       <c r="A15" s="16" t="n">
         <v>2002</v>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>扶摇</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>以风刃攻击单体，击败后自动追击气血最低的敌方。</t>
         </is>
       </c>
-      <c r="D15" s="17" t="n"/>
+      <c r="D15" s="18" t="n"/>
       <c r="G15" s="11" t="n">
         <v>1</v>
       </c>
@@ -1675,17 +1678,17 @@
       <c r="A16" s="16" t="n">
         <v>2003</v>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>罡风</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>召唤罡风横扫多个敌方，造成群体法术伤害。</t>
         </is>
       </c>
-      <c r="D16" s="17" t="n"/>
+      <c r="D16" s="18" t="n"/>
       <c r="G16" s="11" t="n">
         <v>1</v>
       </c>
@@ -1720,17 +1723,17 @@
       <c r="A17" s="16" t="n">
         <v>2004</v>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>乘风</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>乘风而行，将自身速度转化为额外法术伤害。</t>
         </is>
       </c>
-      <c r="D17" s="17" t="n"/>
+      <c r="D17" s="18" t="n"/>
       <c r="G17" s="11" t="n">
         <v>1</v>
       </c>
@@ -1765,17 +1768,17 @@
       <c r="A18" s="16" t="n">
         <v>2005</v>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>裂空</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>双动回合中根据首次行动的不同，第二次行动获得不同增益。</t>
         </is>
       </c>
-      <c r="D18" s="17" t="n"/>
+      <c r="D18" s="18" t="n"/>
       <c r="G18" s="11" t="n">
         <v>1</v>
       </c>
@@ -1810,17 +1813,17 @@
       <c r="A19" s="16" t="n">
         <v>2006</v>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>拂柳</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>柳枝般的轻盈身法，大幅提升物理闪避能力。</t>
         </is>
       </c>
-      <c r="D19" s="17" t="n"/>
+      <c r="D19" s="18" t="n"/>
       <c r="G19" s="11" t="n">
         <v>1</v>
       </c>
@@ -1855,17 +1858,17 @@
       <c r="A20" s="16" t="n">
         <v>2007</v>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>祭风</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C20" s="18" t="inlineStr">
         <is>
           <t>以自身气血为代价，快速积累大量风势加速进入狂风。</t>
         </is>
       </c>
-      <c r="D20" s="17" t="n"/>
+      <c r="D20" s="18" t="n"/>
       <c r="G20" s="11" t="n">
         <v>1</v>
       </c>
@@ -1900,17 +1903,17 @@
       <c r="A21" s="16" t="n">
         <v>2008</v>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>碎空</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>双段风刃切割目标，有概率削弱其法术防御。</t>
         </is>
       </c>
-      <c r="D21" s="17" t="n"/>
+      <c r="D21" s="18" t="n"/>
       <c r="G21" s="11" t="n">
         <v>1</v>
       </c>
@@ -1945,12 +1948,12 @@
       <c r="A22" s="16" t="n">
         <v>2009</v>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>大风起</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C22" s="18" t="inlineStr">
         <is>
           <t>在狂风状态下释放全力风暴，席卷多个敌方。首次释放后可保留第二次行动。</t>
         </is>
@@ -1994,17 +1997,17 @@
       <c r="A23" s="16" t="n">
         <v>3001</v>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>灵泉</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C23" s="18" t="inlineStr">
         <is>
           <t>持续积蓄灵泉之水，友方气血危急时自动消耗灵泉进行治疗。</t>
         </is>
       </c>
-      <c r="D23" s="17" t="n"/>
+      <c r="D23" s="18" t="n"/>
       <c r="E23" s="11" t="n"/>
       <c r="F23" s="11" t="n"/>
       <c r="G23" s="11" t="n">
@@ -2041,17 +2044,17 @@
       <c r="A24" s="16" t="n">
         <v>3002</v>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>甘露</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C24" s="18" t="inlineStr">
         <is>
           <t>以甘露治疗友方并弹射至多个队友，同时修复内伤。</t>
         </is>
       </c>
-      <c r="D24" s="17" t="n"/>
+      <c r="D24" s="18" t="n"/>
       <c r="E24" s="11" t="n"/>
       <c r="F24" s="11" t="n"/>
       <c r="G24" s="11" t="n">
@@ -2088,17 +2091,17 @@
       <c r="A25" s="16" t="n">
         <v>3003</v>
       </c>
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>沧浪</t>
         </is>
       </c>
-      <c r="C25" s="17" t="inlineStr">
+      <c r="C25" s="18" t="inlineStr">
         <is>
           <t>以水流攻击多个敌方，释放后有概率获得灵泉。</t>
         </is>
       </c>
-      <c r="D25" s="17" t="n"/>
+      <c r="D25" s="18" t="n"/>
       <c r="G25" s="11" t="n">
         <v>1</v>
       </c>
@@ -2133,17 +2136,17 @@
       <c r="A26" s="16" t="n">
         <v>3004</v>
       </c>
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>护灵诀</t>
         </is>
       </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="C26" s="18" t="inlineStr">
         <is>
           <t>为全队施加灵气护盾，提升法术防御能力。</t>
         </is>
       </c>
-      <c r="D26" s="17" t="n"/>
+      <c r="D26" s="18" t="n"/>
       <c r="G26" s="11" t="n">
         <v>1</v>
       </c>
@@ -2178,17 +2181,17 @@
       <c r="A27" s="16" t="n">
         <v>3005</v>
       </c>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>潮汐</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C27" s="18" t="inlineStr">
         <is>
           <t>灵泉蕴含潮汐之力，治疗时可触发暴击造成更强治疗效果。</t>
         </is>
       </c>
-      <c r="D27" s="17" t="n"/>
+      <c r="D27" s="18" t="n"/>
       <c r="G27" s="11" t="n">
         <v>1</v>
       </c>
@@ -2223,17 +2226,17 @@
       <c r="A28" s="16" t="n">
         <v>3006</v>
       </c>
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t>明镜止水</t>
         </is>
       </c>
-      <c r="C28" s="17" t="inlineStr">
+      <c r="C28" s="18" t="inlineStr">
         <is>
           <t>为友方附加水镜，受伤后自动回复部分气血。</t>
         </is>
       </c>
-      <c r="D28" s="17" t="n"/>
+      <c r="D28" s="18" t="n"/>
       <c r="G28" s="11" t="n">
         <v>1</v>
       </c>
@@ -2268,17 +2271,17 @@
       <c r="A29" s="16" t="n">
         <v>3007</v>
       </c>
-      <c r="B29" s="17" t="inlineStr">
+      <c r="B29" s="18" t="inlineStr">
         <is>
           <t>渡生</t>
         </is>
       </c>
-      <c r="C29" s="17" t="inlineStr">
+      <c r="C29" s="18" t="inlineStr">
         <is>
           <t>复活一名倒地的友方并回复其气血和内伤。</t>
         </is>
       </c>
-      <c r="D29" s="17" t="n"/>
+      <c r="D29" s="18" t="n"/>
       <c r="G29" s="11" t="n">
         <v>1</v>
       </c>
@@ -2313,17 +2316,17 @@
       <c r="A30" s="16" t="n">
         <v>3008</v>
       </c>
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B30" s="18" t="inlineStr">
         <is>
           <t>断脉</t>
         </is>
       </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="C30" s="18" t="inlineStr">
         <is>
           <t>封锁敌方经脉，大幅削弱其法术伤害输出。</t>
         </is>
       </c>
-      <c r="D30" s="17" t="n"/>
+      <c r="D30" s="18" t="n"/>
       <c r="G30" s="11" t="n">
         <v>1</v>
       </c>
@@ -2358,17 +2361,17 @@
       <c r="A31" s="16" t="n">
         <v>3009</v>
       </c>
-      <c r="B31" s="17" t="inlineStr">
+      <c r="B31" s="18" t="inlineStr">
         <is>
           <t>海纳百川</t>
         </is>
       </c>
-      <c r="C31" s="17" t="inlineStr">
+      <c r="C31" s="18" t="inlineStr">
         <is>
           <t>全队进入共患状态，所有伤害由全体均摊承受。</t>
         </is>
       </c>
-      <c r="D31" s="17" t="n"/>
+      <c r="D31" s="18" t="n"/>
       <c r="G31" s="11" t="n">
         <v>1</v>
       </c>
@@ -2403,17 +2406,17 @@
       <c r="A32" s="16" t="n">
         <v>4001</v>
       </c>
-      <c r="B32" s="17" t="inlineStr">
+      <c r="B32" s="18" t="inlineStr">
         <is>
           <t>画符</t>
         </is>
       </c>
-      <c r="C32" s="17" t="inlineStr">
+      <c r="C32" s="18" t="inlineStr">
         <is>
           <t>定期获得符箓随机强化一个技能，使其获得额外效果。战斗核心在于符箓的分配与运用。</t>
         </is>
       </c>
-      <c r="D32" s="17" t="n"/>
+      <c r="D32" s="18" t="n"/>
       <c r="G32" s="11" t="n">
         <v>1</v>
       </c>
@@ -2448,17 +2451,17 @@
       <c r="A33" s="16" t="n">
         <v>4002</v>
       </c>
-      <c r="B33" s="17" t="inlineStr">
+      <c r="B33" s="18" t="inlineStr">
         <is>
           <t>失心</t>
         </is>
       </c>
-      <c r="C33" s="17" t="inlineStr">
+      <c r="C33" s="18" t="inlineStr">
         <is>
           <t>以符箓封禁敌方法术能力，被强化时额外附加破甲。</t>
         </is>
       </c>
-      <c r="D33" s="17" t="n"/>
+      <c r="D33" s="18" t="n"/>
       <c r="G33" s="11" t="n">
         <v>1</v>
       </c>
@@ -2493,17 +2496,17 @@
       <c r="A34" s="16" t="n">
         <v>4003</v>
       </c>
-      <c r="B34" s="17" t="inlineStr">
+      <c r="B34" s="18" t="inlineStr">
         <is>
           <t>天雷</t>
         </is>
       </c>
-      <c r="C34" s="17" t="inlineStr">
+      <c r="C34" s="18" t="inlineStr">
         <is>
           <t>引天雷攻击多个敌方，有概率封禁首目标法术。被强化时对首目标双重雷击。</t>
         </is>
       </c>
-      <c r="D34" s="17" t="n"/>
+      <c r="D34" s="18" t="n"/>
       <c r="G34" s="11" t="n">
         <v>1</v>
       </c>
@@ -2538,17 +2541,17 @@
       <c r="A35" s="16" t="n">
         <v>4004</v>
       </c>
-      <c r="B35" s="17" t="inlineStr">
+      <c r="B35" s="18" t="inlineStr">
         <is>
           <t>定身术</t>
         </is>
       </c>
-      <c r="C35" s="17" t="inlineStr">
+      <c r="C35" s="18" t="inlineStr">
         <is>
           <t>以定身符缴械敌方禁止物理攻击，被强化后升级为完全定身。</t>
         </is>
       </c>
-      <c r="D35" s="17" t="n"/>
+      <c r="D35" s="18" t="n"/>
       <c r="G35" s="11" t="n">
         <v>1</v>
       </c>
@@ -2583,17 +2586,17 @@
       <c r="A36" s="16" t="n">
         <v>4005</v>
       </c>
-      <c r="B36" s="17" t="inlineStr">
+      <c r="B36" s="18" t="inlineStr">
         <is>
           <t>律令</t>
         </is>
       </c>
-      <c r="C36" s="17" t="inlineStr">
+      <c r="C36" s="18" t="inlineStr">
         <is>
           <t>急急如律令，立即获得额外符箓加速技能强化。每多强化一种技能，封印与防御持续增强。</t>
         </is>
       </c>
-      <c r="D36" s="17" t="n"/>
+      <c r="D36" s="18" t="n"/>
       <c r="G36" s="11" t="n">
         <v>1</v>
       </c>
@@ -2628,17 +2631,17 @@
       <c r="A37" s="16" t="n">
         <v>4006</v>
       </c>
-      <c r="B37" s="17" t="inlineStr">
+      <c r="B37" s="18" t="inlineStr">
         <is>
           <t>斗转</t>
         </is>
       </c>
-      <c r="C37" s="17" t="inlineStr">
+      <c r="C37" s="18" t="inlineStr">
         <is>
           <t>以星移之术扰乱敌方心智，使其攻击转向自身。被强化时可复制目标增益。</t>
         </is>
       </c>
-      <c r="D37" s="17" t="n"/>
+      <c r="D37" s="18" t="n"/>
       <c r="G37" s="11" t="n">
         <v>1</v>
       </c>
@@ -2673,17 +2676,17 @@
       <c r="A38" s="16" t="n">
         <v>4007</v>
       </c>
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B38" s="18" t="inlineStr">
         <is>
           <t>金光咒</t>
         </is>
       </c>
-      <c r="C38" s="17" t="inlineStr">
+      <c r="C38" s="18" t="inlineStr">
         <is>
           <t>诵持金光咒护体，每回合自动获得护盾。被强化后每回合额外净化一个减益。</t>
         </is>
       </c>
-      <c r="D38" s="17" t="n"/>
+      <c r="D38" s="18" t="n"/>
       <c r="G38" s="11" t="n">
         <v>1</v>
       </c>
@@ -2718,17 +2721,17 @@
       <c r="A39" s="16" t="n">
         <v>4008</v>
       </c>
-      <c r="B39" s="17" t="inlineStr">
+      <c r="B39" s="18" t="inlineStr">
         <is>
           <t>断念</t>
         </is>
       </c>
-      <c r="C39" s="17" t="inlineStr">
+      <c r="C39" s="18" t="inlineStr">
         <is>
           <t>以念力延长敌方身上所有减益的持续时间，被强化后连不可驱散减益也能延长。</t>
         </is>
       </c>
-      <c r="D39" s="17" t="n"/>
+      <c r="D39" s="18" t="n"/>
       <c r="G39" s="11" t="n">
         <v>1</v>
       </c>
@@ -2763,12 +2766,12 @@
       <c r="A40" s="16" t="n">
         <v>4009</v>
       </c>
-      <c r="B40" s="17" t="inlineStr">
+      <c r="B40" s="18" t="inlineStr">
         <is>
           <t>夺魄</t>
         </is>
       </c>
-      <c r="C40" s="17" t="inlineStr">
+      <c r="C40" s="18" t="inlineStr">
         <is>
           <t>以强大的精神力混乱敌方心智，使其行为完全失控。</t>
         </is>
@@ -2807,17 +2810,17 @@
       <c r="A41" s="16" t="n">
         <v>5001</v>
       </c>
-      <c r="B41" s="17" t="inlineStr">
+      <c r="B41" s="18" t="inlineStr">
         <is>
           <t>御兽</t>
         </is>
       </c>
-      <c r="C41" s="17" t="inlineStr">
+      <c r="C41" s="18" t="inlineStr">
         <is>
           <t>定期感召灵兽之力，每2回合结束时获得1个随机宠物被动技能加持，倒地时消散2个技能，至多拥有3个技能</t>
         </is>
       </c>
-      <c r="D41" s="17" t="n"/>
+      <c r="D41" s="18" t="n"/>
       <c r="G41" s="11" t="n">
         <v>1</v>
       </c>
@@ -2852,17 +2855,17 @@
       <c r="A42" s="16" t="n">
         <v>5002</v>
       </c>
-      <c r="B42" s="17" t="inlineStr">
+      <c r="B42" s="18" t="inlineStr">
         <is>
           <t>裂地枪</t>
         </is>
       </c>
-      <c r="C42" s="17" t="inlineStr">
+      <c r="C42" s="18" t="inlineStr">
         <is>
           <t>以大开大合的枪法横扫全场多个敌方，释放后需休息。</t>
         </is>
       </c>
-      <c r="D42" s="17" t="n"/>
+      <c r="D42" s="18" t="n"/>
       <c r="G42" s="11" t="n">
         <v>1</v>
       </c>
@@ -2897,17 +2900,17 @@
       <c r="A43" s="16" t="n">
         <v>5003</v>
       </c>
-      <c r="B43" s="17" t="inlineStr">
+      <c r="B43" s="18" t="inlineStr">
         <is>
           <t>啸天</t>
         </is>
       </c>
-      <c r="C43" s="17" t="inlineStr">
+      <c r="C43" s="18" t="inlineStr">
         <is>
           <t>全力突刺单体造成高额伤害，击败敌方时有机会感召新的灵兽之力。</t>
         </is>
       </c>
-      <c r="D43" s="17" t="n"/>
+      <c r="D43" s="18" t="n"/>
       <c r="G43" s="11" t="n">
         <v>1</v>
       </c>
@@ -2942,17 +2945,17 @@
       <c r="A44" s="16" t="n">
         <v>5004</v>
       </c>
-      <c r="B44" s="17" t="inlineStr">
+      <c r="B44" s="18" t="inlineStr">
         <is>
           <t>共鸣</t>
         </is>
       </c>
-      <c r="C44" s="17" t="inlineStr">
+      <c r="C44" s="18" t="inlineStr">
         <is>
           <t>与宠物建立灵犀共鸣，共享攻击力并互相分担伤害。</t>
         </is>
       </c>
-      <c r="D44" s="17" t="n"/>
+      <c r="D44" s="18" t="n"/>
       <c r="G44" s="11" t="n">
         <v>1</v>
       </c>
@@ -2987,17 +2990,17 @@
       <c r="A45" s="16" t="n">
         <v>5005</v>
       </c>
-      <c r="B45" s="17" t="inlineStr">
+      <c r="B45" s="18" t="inlineStr">
         <is>
           <t>龙脉</t>
         </is>
       </c>
-      <c r="C45" s="17" t="inlineStr">
+      <c r="C45" s="18" t="inlineStr">
         <is>
           <t>灵兽血脉觉醒，可容纳更多宠物技能，相同技能可升级为高级版本。</t>
         </is>
       </c>
-      <c r="D45" s="17" t="n"/>
+      <c r="D45" s="18" t="n"/>
       <c r="G45" s="11" t="n">
         <v>1</v>
       </c>
@@ -3032,17 +3035,17 @@
       <c r="A46" s="16" t="n">
         <v>5006</v>
       </c>
-      <c r="B46" s="17" t="inlineStr">
+      <c r="B46" s="18" t="inlineStr">
         <is>
           <t>舍身</t>
         </is>
       </c>
-      <c r="C46" s="17" t="inlineStr">
+      <c r="C46" s="18" t="inlineStr">
         <is>
           <t>舍弃防御换取穿透之力，气血越低穿透越强，绝境爆发。</t>
         </is>
       </c>
-      <c r="D46" s="17" t="n"/>
+      <c r="D46" s="18" t="n"/>
       <c r="G46" s="11" t="n">
         <v>1</v>
       </c>
@@ -3077,17 +3080,17 @@
       <c r="A47" s="16" t="n">
         <v>5007</v>
       </c>
-      <c r="B47" s="17" t="inlineStr">
+      <c r="B47" s="18" t="inlineStr">
         <is>
           <t>骤雨</t>
         </is>
       </c>
-      <c r="C47" s="17" t="inlineStr">
+      <c r="C47" s="18" t="inlineStr">
         <is>
           <t>消耗灵兽技能发动枪法连击，攻击后立即获得新的技能替换。</t>
         </is>
       </c>
-      <c r="D47" s="17" t="n"/>
+      <c r="D47" s="18" t="n"/>
       <c r="G47" s="11" t="n">
         <v>1</v>
       </c>
@@ -3122,17 +3125,17 @@
       <c r="A48" s="16" t="n">
         <v>5008</v>
       </c>
-      <c r="B48" s="17" t="inlineStr">
+      <c r="B48" s="18" t="inlineStr">
         <is>
           <t>天崩</t>
         </is>
       </c>
-      <c r="C48" s="17" t="inlineStr">
+      <c r="C48" s="18" t="inlineStr">
         <is>
           <t>将所有灵兽之力凝聚一击，持有技能越多伤害段数越多。</t>
         </is>
       </c>
-      <c r="D48" s="17" t="n"/>
+      <c r="D48" s="18" t="n"/>
       <c r="G48" s="11" t="n">
         <v>1</v>
       </c>
@@ -3167,12 +3170,12 @@
       <c r="A49" s="16" t="n">
         <v>5009</v>
       </c>
-      <c r="B49" s="17" t="inlineStr">
+      <c r="B49" s="18" t="inlineStr">
         <is>
           <t>神龙摆尾</t>
         </is>
       </c>
-      <c r="C49" s="17" t="inlineStr">
+      <c r="C49" s="18" t="inlineStr">
         <is>
           <t>吸收共鸣宠物化为己身，大幅提升属性并攻击多个敌方。</t>
         </is>
@@ -3211,12 +3214,12 @@
       <c r="A50" s="16" t="n">
         <v>6001</v>
       </c>
-      <c r="B50" s="17" t="inlineStr">
+      <c r="B50" s="18" t="inlineStr">
         <is>
           <t>三昧真火</t>
         </is>
       </c>
-      <c r="C50" s="17" t="inlineStr">
+      <c r="C50" s="18" t="inlineStr">
         <is>
           <t>施法时自动积蓄火球，火球满溢时自动攻击随机敌方，是所有火系技能的基础。</t>
         </is>
@@ -3255,12 +3258,12 @@
       <c r="A51" s="16" t="n">
         <v>6002</v>
       </c>
-      <c r="B51" s="17" t="inlineStr">
+      <c r="B51" s="18" t="inlineStr">
         <is>
           <t>红莲</t>
         </is>
       </c>
-      <c r="C51" s="17" t="inlineStr">
+      <c r="C51" s="18" t="inlineStr">
         <is>
           <t>释放两枚火球顺次攻击敌方，同时积蓄新的火球，攻守兼备。</t>
         </is>
@@ -3299,12 +3302,12 @@
       <c r="A52" s="16" t="n">
         <v>6003</v>
       </c>
-      <c r="B52" s="17" t="inlineStr">
+      <c r="B52" s="18" t="inlineStr">
         <is>
           <t>赤焰</t>
         </is>
       </c>
-      <c r="C52" s="17" t="inlineStr">
+      <c r="C52" s="18" t="inlineStr">
         <is>
           <t>消耗积蓄的火球释放群体烈焰，消耗越多范围越大、伤害越高。</t>
         </is>
@@ -3343,12 +3346,12 @@
       <c r="A53" s="16" t="n">
         <v>6004</v>
       </c>
-      <c r="B53" s="17" t="inlineStr">
+      <c r="B53" s="18" t="inlineStr">
         <is>
           <t>浴火</t>
         </is>
       </c>
-      <c r="C53" s="17" t="inlineStr">
+      <c r="C53" s="18" t="inlineStr">
         <is>
           <t>以气血和魔法为代价持续燃烧自身，稳定产出火球为后续爆发蓄力。</t>
         </is>
@@ -3387,12 +3390,12 @@
       <c r="A54" s="16" t="n">
         <v>6005</v>
       </c>
-      <c r="B54" s="17" t="inlineStr">
+      <c r="B54" s="18" t="inlineStr">
         <is>
           <t>薪火</t>
         </is>
       </c>
-      <c r="C54" s="17" t="inlineStr">
+      <c r="C54" s="18" t="inlineStr">
         <is>
           <t>消耗火球时将火焰之力传递给宠物，持续强化其战斗能力。</t>
         </is>
@@ -3431,12 +3434,12 @@
       <c r="A55" s="16" t="n">
         <v>6006</v>
       </c>
-      <c r="B55" s="17" t="inlineStr">
+      <c r="B55" s="18" t="inlineStr">
         <is>
           <t>陨星坠</t>
         </is>
       </c>
-      <c r="C55" s="17" t="inlineStr">
+      <c r="C55" s="18" t="inlineStr">
         <is>
           <t>消耗火球凝聚为陨星砸向单体，造成多段法术伤害。</t>
         </is>
@@ -3475,12 +3478,12 @@
       <c r="A56" s="16" t="n">
         <v>6007</v>
       </c>
-      <c r="B56" s="17" t="inlineStr">
+      <c r="B56" s="18" t="inlineStr">
         <is>
           <t>天赐</t>
         </is>
       </c>
-      <c r="C56" s="17" t="inlineStr">
+      <c r="C56" s="18" t="inlineStr">
         <is>
           <t>暂时扩大火球容量并提升法术伤害，为后续爆发创造条件。</t>
         </is>
@@ -3519,12 +3522,12 @@
       <c r="A57" s="16" t="n">
         <v>6008</v>
       </c>
-      <c r="B57" s="17" t="inlineStr">
+      <c r="B57" s="18" t="inlineStr">
         <is>
           <t>炎盾</t>
         </is>
       </c>
-      <c r="C57" s="17" t="inlineStr">
+      <c r="C57" s="18" t="inlineStr">
         <is>
           <t>凝聚火焰护盾抵御物理伤害，攻击者有概率被灼烧反噬。</t>
         </is>
@@ -3563,12 +3566,12 @@
       <c r="A58" s="16" t="n">
         <v>6009</v>
       </c>
-      <c r="B58" s="17" t="inlineStr">
+      <c r="B58" s="18" t="inlineStr">
         <is>
           <t>焚天</t>
         </is>
       </c>
-      <c r="C58" s="17" t="inlineStr">
+      <c r="C58" s="18" t="inlineStr">
         <is>
           <t>引爆所有火球化为焚天烈焰，火球越多伤害段数越多。</t>
         </is>
@@ -3607,12 +3610,12 @@
       <c r="A59" s="16" t="n">
         <v>7001</v>
       </c>
-      <c r="B59" s="17" t="inlineStr">
+      <c r="B59" s="18" t="inlineStr">
         <is>
           <t>生生不息</t>
         </is>
       </c>
-      <c r="C59" s="17" t="inlineStr">
+      <c r="C59" s="18" t="inlineStr">
         <is>
           <t>治疗时为友方附加持续回血的「生息」效果，生生不息源源回复。</t>
         </is>
@@ -3651,12 +3654,12 @@
       <c r="A60" s="16" t="n">
         <v>7002</v>
       </c>
-      <c r="B60" s="17" t="inlineStr">
+      <c r="B60" s="18" t="inlineStr">
         <is>
           <t>回春术</t>
         </is>
       </c>
-      <c r="C60" s="17" t="inlineStr">
+      <c r="C60" s="18" t="inlineStr">
         <is>
           <t>以强大的回春之力治疗单体友方，同时修复大量内伤。</t>
         </is>
@@ -3695,12 +3698,12 @@
       <c r="A61" s="16" t="n">
         <v>7003</v>
       </c>
-      <c r="B61" s="17" t="inlineStr">
+      <c r="B61" s="18" t="inlineStr">
         <is>
           <t>飞花</t>
         </is>
       </c>
-      <c r="C61" s="17" t="inlineStr">
+      <c r="C61" s="18" t="inlineStr">
         <is>
           <t>以花瓣化作法力攻击多个敌方，有概率为最虚弱的友方附加持续回血。</t>
         </is>
@@ -3739,12 +3742,12 @@
       <c r="A62" s="16" t="n">
         <v>7004</v>
       </c>
-      <c r="B62" s="17" t="inlineStr">
+      <c r="B62" s="18" t="inlineStr">
         <is>
           <t>铁壁</t>
         </is>
       </c>
-      <c r="C62" s="17" t="inlineStr">
+      <c r="C62" s="18" t="inlineStr">
         <is>
           <t>为全队施加铁壁护甲，提升物理防御能力。</t>
         </is>
@@ -3783,12 +3786,12 @@
       <c r="A63" s="16" t="n">
         <v>7005</v>
       </c>
-      <c r="B63" s="17" t="inlineStr">
+      <c r="B63" s="18" t="inlineStr">
         <is>
           <t>绽放</t>
         </is>
       </c>
-      <c r="C63" s="17" t="inlineStr">
+      <c r="C63" s="18" t="inlineStr">
         <is>
           <t>生息到期时有概率绽放，一次性回复大量气血。</t>
         </is>
@@ -3827,12 +3830,12 @@
       <c r="A64" s="16" t="n">
         <v>7006</v>
       </c>
-      <c r="B64" s="17" t="inlineStr">
+      <c r="B64" s="18" t="inlineStr">
         <is>
           <t>醍醐</t>
         </is>
       </c>
-      <c r="C64" s="17" t="inlineStr">
+      <c r="C64" s="18" t="inlineStr">
         <is>
           <t>立即引爆全队所有生息，将积累的治疗量一次性释放。</t>
         </is>
@@ -3871,12 +3874,12 @@
       <c r="A65" s="16" t="n">
         <v>7007</v>
       </c>
-      <c r="B65" s="17" t="inlineStr">
+      <c r="B65" s="18" t="inlineStr">
         <is>
           <t>逢春</t>
         </is>
       </c>
-      <c r="C65" s="17" t="inlineStr">
+      <c r="C65" s="18" t="inlineStr">
         <is>
           <t>复活一名倒地友方并附加生息持续回血。</t>
         </is>
@@ -3915,12 +3918,12 @@
       <c r="A66" s="16" t="n">
         <v>7008</v>
       </c>
-      <c r="B66" s="17" t="inlineStr">
+      <c r="B66" s="18" t="inlineStr">
         <is>
           <t>枯荣</t>
         </is>
       </c>
-      <c r="C66" s="17" t="inlineStr">
+      <c r="C66" s="18" t="inlineStr">
         <is>
           <t>以枯荣之力削弱敌方，大幅降低其物理伤害输出。</t>
         </is>
@@ -3959,12 +3962,12 @@
       <c r="A67" s="16" t="n">
         <v>7009</v>
       </c>
-      <c r="B67" s="17" t="inlineStr">
+      <c r="B67" s="18" t="inlineStr">
         <is>
           <t>万象复苏</t>
         </is>
       </c>
-      <c r="C67" s="17" t="inlineStr">
+      <c r="C67" s="18" t="inlineStr">
         <is>
           <t>复活全体倒地友方并回复气血和内伤。</t>
         </is>
@@ -4003,12 +4006,12 @@
       <c r="A68" s="16" t="n">
         <v>8001</v>
       </c>
-      <c r="B68" s="17" t="inlineStr">
+      <c r="B68" s="18" t="inlineStr">
         <is>
           <t>化形</t>
         </is>
       </c>
-      <c r="C68" s="17" t="inlineStr">
+      <c r="C68" s="18" t="inlineStr">
         <is>
           <t>封印成功后有概率使宠物获得灵兽化形，不同化形提供不同属性加成。</t>
         </is>
@@ -4047,12 +4050,12 @@
       <c r="A69" s="16" t="n">
         <v>8002</v>
       </c>
-      <c r="B69" s="17" t="inlineStr">
+      <c r="B69" s="18" t="inlineStr">
         <is>
           <t>醉生梦死</t>
         </is>
       </c>
-      <c r="C69" s="17" t="inlineStr">
+      <c r="C69" s="18" t="inlineStr">
         <is>
           <t>以梦蝶同时封禁两个敌方的法术能力，次目标命中率较低。</t>
         </is>
@@ -4091,12 +4094,12 @@
       <c r="A70" s="16" t="n">
         <v>8003</v>
       </c>
-      <c r="B70" s="17" t="inlineStr">
+      <c r="B70" s="18" t="inlineStr">
         <is>
           <t>霓裳</t>
         </is>
       </c>
-      <c r="C70" s="17" t="inlineStr">
+      <c r="C70" s="18" t="inlineStr">
         <is>
           <t>以幻彩霓裳攻击多个敌方，有概率封禁首目标法术。</t>
         </is>
@@ -4135,12 +4138,12 @@
       <c r="A71" s="16" t="n">
         <v>8004</v>
       </c>
-      <c r="B71" s="17" t="inlineStr">
+      <c r="B71" s="18" t="inlineStr">
         <is>
           <t>幻惑</t>
         </is>
       </c>
-      <c r="C71" s="17" t="inlineStr">
+      <c r="C71" s="18" t="inlineStr">
         <is>
           <t>以幻术惑心，禁止敌方获得新增益并逐步剥离已有增益。</t>
         </is>
@@ -4179,12 +4182,12 @@
       <c r="A72" s="16" t="n">
         <v>8005</v>
       </c>
-      <c r="B72" s="17" t="inlineStr">
+      <c r="B72" s="18" t="inlineStr">
         <is>
           <t>擅变</t>
         </is>
       </c>
-      <c r="C72" s="17" t="inlineStr">
+      <c r="C72" s="18" t="inlineStr">
         <is>
           <t>化形时自动匹配属性最适合的宠物，使加成效果最大化。</t>
         </is>
@@ -4223,12 +4226,12 @@
       <c r="A73" s="16" t="n">
         <v>8006</v>
       </c>
-      <c r="B73" s="17" t="inlineStr">
+      <c r="B73" s="18" t="inlineStr">
         <is>
           <t>妖雾</t>
         </is>
       </c>
-      <c r="C73" s="17" t="inlineStr">
+      <c r="C73" s="18" t="inlineStr">
         <is>
           <t>散出妖雾环身，大幅提升物理和法术闪避能力。</t>
         </is>
@@ -4267,12 +4270,12 @@
       <c r="A74" s="16" t="n">
         <v>8007</v>
       </c>
-      <c r="B74" s="17" t="inlineStr">
+      <c r="B74" s="18" t="inlineStr">
         <is>
           <t>绝息</t>
         </is>
       </c>
-      <c r="C74" s="17" t="inlineStr">
+      <c r="C74" s="18" t="inlineStr">
         <is>
           <t>以妖力封锁敌方人物的门派被动技能，釜底抽薪。</t>
         </is>
@@ -4311,12 +4314,12 @@
       <c r="A75" s="16" t="n">
         <v>8008</v>
       </c>
-      <c r="B75" s="17" t="inlineStr">
+      <c r="B75" s="18" t="inlineStr">
         <is>
           <t>裂魂爪</t>
         </is>
       </c>
-      <c r="C75" s="17" t="inlineStr">
+      <c r="C75" s="18" t="inlineStr">
         <is>
           <t>以妖爪攻击造成固定伤害并附加重伤，削弱敌方被治疗效果。</t>
         </is>
@@ -4355,12 +4358,12 @@
       <c r="A76" s="16" t="n">
         <v>8009</v>
       </c>
-      <c r="B76" s="17" t="inlineStr">
+      <c r="B76" s="18" t="inlineStr">
         <is>
           <t>上古妖形</t>
         </is>
       </c>
-      <c r="C76" s="17" t="inlineStr">
+      <c r="C76" s="18" t="inlineStr">
         <is>
           <t>释放太古之力将所有宠物化形进化为上古神兽，获得极强属性加成。</t>
         </is>
@@ -4422,6 +4425,16 @@
           <t>TRY_CHANGE2</t>
         </is>
       </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="n">
+        <v>8011</v>
+      </c>
+      <c r="B78" s="0" t="n"/>
+      <c r="C78" s="0" t="n"/>
+      <c r="G78" s="0" t="n"/>
+      <c r="H78" s="0" t="n"/>
+      <c r="K78" s="0" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4 A77:A1048576">

--- a/resources/school/school_ability.xlsx
+++ b/resources/school/school_ability.xlsx
@@ -4454,7 +4454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="18.375" customWidth="1" style="8" min="1" max="2"/>
@@ -6049,6 +6049,70 @@
       </c>
       <c r="G79" s="0" t="n">
         <v>901</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="n">
+        <v>8010003</v>
+      </c>
+      <c r="B80" s="0" t="n"/>
+      <c r="C80" s="0" t="n"/>
+      <c r="D80" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="0" t="n">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="n">
+        <v>8010004</v>
+      </c>
+      <c r="B81" s="0" t="n"/>
+      <c r="C81" s="0" t="n"/>
+      <c r="D81" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="0" t="n">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="n">
+        <v>8010005</v>
+      </c>
+      <c r="B82" s="0" t="n"/>
+      <c r="C82" s="0" t="n"/>
+      <c r="D82" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="0" t="n">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="0" t="n">
+        <v>8010006</v>
+      </c>
+      <c r="B83" s="0" t="n"/>
+      <c r="C83" s="0" t="n"/>
+      <c r="D83" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="0" t="n">
+        <v>904</v>
       </c>
     </row>
   </sheetData>

--- a/resources/school/school_ability.xlsx
+++ b/resources/school/school_ability.xlsx
@@ -989,7 +989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
@@ -4436,6 +4436,22 @@
       <c r="H78" s="0" t="n"/>
       <c r="K78" s="0" t="n"/>
     </row>
+    <row r="79">
+      <c r="A79" s="0" t="n">
+        <v>9001</v>
+      </c>
+      <c r="B79" s="0" t="inlineStr">
+        <is>
+          <t>焚天决</t>
+        </is>
+      </c>
+      <c r="C79" s="0" t="n"/>
+      <c r="G79" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" s="0" t="n"/>
+      <c r="K79" s="0" t="n"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4 A77:A1048576">
     <cfRule type="duplicateValues" priority="1" dxfId="0"/>
@@ -4454,7 +4470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="18.375" customWidth="1" style="8" min="1" max="2"/>
@@ -6113,6 +6129,46 @@
       </c>
       <c r="G83" s="0" t="n">
         <v>904</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="0" t="n">
+        <v>9001000</v>
+      </c>
+      <c r="B84" s="0" t="n">
+        <v>9001</v>
+      </c>
+      <c r="C84" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="0" t="n">
+        <v>8600</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="0" t="n">
+        <v>9001001</v>
+      </c>
+      <c r="B85" s="0" t="n">
+        <v>9001</v>
+      </c>
+      <c r="C85" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E85" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="G85" s="0" t="n">
+        <v>8601</v>
       </c>
     </row>
   </sheetData>
